--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1837,10 +1837,10 @@
         <v>18</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>18</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1994,22 +1994,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -2072,22 +2072,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -2150,22 +2150,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2228,22 +2228,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -9513,45 +9513,45 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
         <is>
           <t>A1-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr"/>
+      <c r="H183" s="9" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10746,45 +10746,45 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
         <is>
           <t>A1-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr"/>
+      <c r="H210" s="9" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I210" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I210" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11979,45 +11979,49 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>A1-E1</t>
         </is>
       </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
-      <c r="H237" s="5" t="inlineStr">
-        <is>
-          <t>0/38</t>
-        </is>
-      </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>36/38</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13212,45 +13216,49 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="5" t="inlineStr">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>A1-E2</t>
         </is>
       </c>
-      <c r="C264" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E264" s="5" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr"/>
-      <c r="H264" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I264" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>34/39</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14445,45 +14453,49 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="5" t="inlineStr">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>A1-F1</t>
         </is>
       </c>
-      <c r="C291" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="5" t="inlineStr">
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E291" s="5" t="inlineStr">
+      <c r="E291" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="5" t="inlineStr"/>
-      <c r="H291" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I291" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>34/39</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15674,45 +15686,49 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="5" t="inlineStr">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
         <is>
           <t>A1-F2</t>
         </is>
       </c>
-      <c r="C318" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E318" s="5" t="inlineStr">
+      <c r="E318" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr"/>
-      <c r="H318" s="5" t="inlineStr">
-        <is>
-          <t>0/39</t>
-        </is>
-      </c>
-      <c r="I318" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>32/39</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
